--- a/excel_routes/route_DMM_CAI_threats.xlsx
+++ b/excel_routes/route_DMM_CAI_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-432</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1419</v>
+        <v>1389</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1696</v>
+        <v>2116</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-277</v>
+        <v>-727</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>flynas XY-854</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1429</v>
+        <v>1389</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1696</v>
+        <v>2116</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-267</v>
+        <v>-727</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-132</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1653</v>
+        <v>1419</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1696</v>
+        <v>2116</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-43</v>
+        <v>-697</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-334</t>
+          <t>Nile Air NP-132</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1653</v>
+        <v>1419</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1696</v>
+        <v>2116</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-43</v>
+        <v>-697</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-153</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1669</v>
+        <v>1429</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1696</v>
+        <v>2116</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-27</v>
+        <v>-687</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>24-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-432</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1419</v>
+        <v>1549</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>2116</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-697</v>
+        <v>-567</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        <v>15</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MEDIUM THREAT - MONITOR</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>Nile Air NP-132</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1653</v>
+        <v>1419</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>2116</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-463</v>
+        <v>-697</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-132</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1653</v>
+        <v>1429</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>2116</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-463</v>
+        <v>-687</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>Nile Air NP-332</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1999</v>
+        <v>1653</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>2116</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-117</v>
+        <v>-463</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>19-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2019</v>
+        <v>2045</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>2116</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-97</v>
+        <v>-71</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>26-MAR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>flynas XY-854</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1249</v>
+        <v>2089</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1456</v>
+        <v>2116</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-207</v>
+        <v>-27</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1456</v>
+        <v>2116</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-37</v>
+        <v>-687</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20-MAR-26</t>
+          <t>27-MAR-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-153</t>
+          <t>Nile Air NP-132</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1429</v>
+        <v>1653</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1456</v>
+        <v>2116</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-27</v>
+        <v>-463</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1112,12 +1112,1992 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-463</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>27-MAR-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>28-MAR-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-611</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>28-MAR-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-132</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-573</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>28-MAR-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-854</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-567</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>28-MAR-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2319</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-337</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-234</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-1603</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-1211</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-1173</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>2669</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-587</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3467</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3467</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-682</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3467</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3256</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-234</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-463</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-71</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>30-MAR-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-332</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>2116</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1849</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-807</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-573</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-132</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-573</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-151</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2089</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-567</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2669</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-911</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2045</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-611</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-232</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2083</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-573</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-894</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2299</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-357</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-316</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2307</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2656</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-349</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>994</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1036</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>994</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>994</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>994</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-316</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>667</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-159</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-151</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>670</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-156</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-48</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>08-APR-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>778</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>736</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>14-APR-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-151</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-236</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>14-APR-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-688</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>14-APR-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-682</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>14-APR-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-684</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>15-APR-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-434</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>17-APR-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-440</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-698</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>634</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_DMM_CAI_threats.xlsx
+++ b/excel_routes/route_DMM_CAI_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J132" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="J188" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J196" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J198" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="J216" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="J222" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="J224" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="J228" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J241" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J242" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J243" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="J244" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="J245" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="J246" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J247" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="J248" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="J249" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J251" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J253" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="J254" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="J255" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="J256" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J257" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J258" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J259" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J260" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J261" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="J262" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="J263" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="J264" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="J265" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="J266" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J267" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="J268" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="J269" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K269" s="2" t="inlineStr">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="J270" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K270" s="2" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="J271" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="J272" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K272" s="2" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="J273" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K273" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="J274" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="J275" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="J276" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="J277" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="J278" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="J279" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="J280" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="J281" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="J282" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="J283" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="J284" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="J285" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="J286" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="J287" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="J288" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="J289" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="J290" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="J291" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K291" s="2" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="J292" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K292" s="2" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="J293" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="J294" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="J295" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K295" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="J296" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="J297" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="J298" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="J299" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="J300" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="J301" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="J302" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="J303" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="J304" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="J305" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="J306" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="J307" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="J308" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="J309" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="J310" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="J311" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K311" s="2" t="inlineStr">
@@ -14524,7 +14524,7 @@
       </c>
       <c r="J312" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="J313" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K313" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="J314" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="J315" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K315" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="J316" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="J317" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="J318" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K318" s="2" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="J319" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="J320" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K320" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="J321" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K321" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="J322" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K322" s="2" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="J323" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="J324" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="J325" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -15154,7 +15154,7 @@
       </c>
       <c r="J326" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="J327" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K327" s="2" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="J328" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="J329" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="J330" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="J331" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="J332" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K332" s="2" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="J333" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="J334" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K334" s="2" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="J335" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K335" s="2" t="inlineStr">
@@ -15604,7 +15604,7 @@
       </c>
       <c r="J336" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K336" s="2" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="J337" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K337" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="J338" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K338" s="2" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="J339" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="J340" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="J341" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K341" s="2" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="J342" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K342" s="2" t="inlineStr">
@@ -15919,7 +15919,7 @@
       </c>
       <c r="J343" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K343" s="2" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="J344" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K344" s="2" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="J345" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K345" s="2" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="J346" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K346" s="2" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="J347" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K347" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="J348" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K348" s="2" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="J349" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K349" s="2" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="J350" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K350" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="J351" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="J352" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -16369,7 +16369,7 @@
       </c>
       <c r="J353" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K353" s="2" t="inlineStr">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="J354" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K354" s="2" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="J355" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K355" s="2" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="J356" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -16549,7 +16549,7 @@
       </c>
       <c r="J357" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K357" s="2" t="inlineStr">
@@ -16594,7 +16594,7 @@
       </c>
       <c r="J358" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="J359" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="J360" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K360" s="2" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="J361" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K361" s="2" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="J362" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K362" s="2" t="inlineStr">
@@ -16819,7 +16819,7 @@
       </c>
       <c r="J363" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K363" s="2" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="J364" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K364" s="2" t="inlineStr">
@@ -16909,7 +16909,7 @@
       </c>
       <c r="J365" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K365" s="2" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="J366" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K366" s="2" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="J367" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K367" s="2" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="J368" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K368" s="2" t="inlineStr">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J369" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K369" s="2" t="inlineStr">
@@ -17134,7 +17134,7 @@
       </c>
       <c r="J370" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K370" s="2" t="inlineStr">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="J371" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K371" s="2" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="J372" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K372" s="2" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="J373" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K373" s="2" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="J374" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K374" s="2" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="J375" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K375" s="2" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="J376" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K376" s="2" t="inlineStr">
@@ -17449,7 +17449,7 @@
       </c>
       <c r="J377" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="J378" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K378" s="2" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="J379" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K379" s="2" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="J380" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K380" s="2" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="J381" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K381" s="2" t="inlineStr">
@@ -17674,7 +17674,7 @@
       </c>
       <c r="J382" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K382" s="2" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="J383" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K383" s="2" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="J384" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K384" s="2" t="inlineStr">
@@ -17809,7 +17809,7 @@
       </c>
       <c r="J385" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K385" s="2" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="J386" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K386" s="2" t="inlineStr">
@@ -17899,7 +17899,7 @@
       </c>
       <c r="J387" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K387" s="2" t="inlineStr">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="J388" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="J389" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K389" s="2" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="J390" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="J391" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K391" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="J392" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="J393" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="J394" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K394" s="2" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="J395" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K395" s="2" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="J396" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K396" s="2" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="J397" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K397" s="2" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="J398" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K398" s="2" t="inlineStr">
@@ -18439,7 +18439,7 @@
       </c>
       <c r="J399" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K399" s="2" t="inlineStr">
@@ -18484,7 +18484,7 @@
       </c>
       <c r="J400" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K400" s="2" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="J401" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K401" s="2" t="inlineStr">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="J402" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K402" s="2" t="inlineStr">
@@ -18619,7 +18619,7 @@
       </c>
       <c r="J403" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K403" s="2" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="J404" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="J405" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K405" s="2" t="inlineStr">
@@ -18754,7 +18754,7 @@
       </c>
       <c r="J406" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K406" s="2" t="inlineStr">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="J407" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K407" s="2" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="J408" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K408" s="2" t="inlineStr">
@@ -18889,7 +18889,7 @@
       </c>
       <c r="J409" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K409" s="2" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="J410" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K410" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="J411" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K411" s="2" t="inlineStr">
@@ -19024,7 +19024,7 @@
       </c>
       <c r="J412" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K412" s="2" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="J413" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K413" s="2" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="J414" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K414" s="2" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="J415" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K415" s="2" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="J416" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K416" s="2" t="inlineStr">
@@ -19249,7 +19249,7 @@
       </c>
       <c r="J417" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K417" s="2" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="J418" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K418" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="J419" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K419" s="2" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="J420" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K420" s="2" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="J421" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K421" s="2" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="J422" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K422" s="2" t="inlineStr">
@@ -19519,7 +19519,7 @@
       </c>
       <c r="J423" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K423" s="2" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="J424" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K424" s="2" t="inlineStr">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="J425" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K425" s="2" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="J426" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K426" s="2" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="J427" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K427" s="2" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="J428" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K428" s="2" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="J429" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K429" s="2" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="J430" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K430" s="2" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="J431" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K431" s="2" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="J432" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K432" s="2" t="inlineStr">
@@ -19969,7 +19969,7 @@
       </c>
       <c r="J433" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="J434" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K434" s="2" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="J435" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K435" s="2" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="J436" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K436" s="2" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="J437" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K437" s="2" t="inlineStr">
@@ -20194,7 +20194,7 @@
       </c>
       <c r="J438" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K438" s="2" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="J439" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K439" s="2" t="inlineStr">
@@ -20284,7 +20284,7 @@
       </c>
       <c r="J440" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K440" s="2" t="inlineStr">
@@ -20329,7 +20329,7 @@
       </c>
       <c r="J441" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K441" s="2" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="J442" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K442" s="2" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="J443" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K443" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="J444" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K444" s="2" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="J445" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K445" s="2" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="J446" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K446" s="2" t="inlineStr">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="J447" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K447" s="2" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="J448" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K448" s="2" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="J449" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K449" s="2" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="J450" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K450" s="2" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K451" s="2" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K452" s="2" t="inlineStr">
@@ -20869,7 +20869,7 @@
       </c>
       <c r="J453" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K453" s="2" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K454" s="2" t="inlineStr">
@@ -20959,7 +20959,7 @@
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K455" s="2" t="inlineStr">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K456" s="2" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K457" s="2" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K458" s="2" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K459" s="2" t="inlineStr">
@@ -21184,7 +21184,7 @@
       </c>
       <c r="J460" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K460" s="2" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K461" s="2" t="inlineStr">
@@ -21274,7 +21274,7 @@
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -21319,7 +21319,7 @@
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K463" s="2" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K464" s="2" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K465" s="2" t="inlineStr">
@@ -21454,7 +21454,7 @@
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K466" s="2" t="inlineStr">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="J467" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K467" s="2" t="inlineStr">
@@ -21544,7 +21544,7 @@
       </c>
       <c r="J468" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K468" s="2" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K469" s="2" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="J470" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K470" s="2" t="inlineStr">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K471" s="2" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K472" s="2" t="inlineStr">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="J473" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K473" s="2" t="inlineStr">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="J474" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K474" s="2" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K475" s="2" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K476" s="2" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="J477" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K479" s="2" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K480" s="2" t="inlineStr">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K481" s="2" t="inlineStr">
@@ -22174,7 +22174,7 @@
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K482" s="2" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K483" s="2" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr">
@@ -22309,7 +22309,7 @@
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="J486" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="J487" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr">

--- a/excel_routes/route_DMM_CAI_threats.xlsx
+++ b/excel_routes/route_DMM_CAI_threats.xlsx
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-432</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1231</v>
+        <v>1140</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-68</v>
+        <v>-159</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -582,22 +582,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-440</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-432</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1231</v>
+        <v>1140</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1455</v>
+        <v>1299</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-224</v>
+        <v>-159</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -608,9 +608,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1409</v>
+        <v>1140</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-46</v>
+        <v>-3</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1409</v>
+        <v>1140</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-46</v>
+        <v>-3</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -712,27 +712,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-440</t>
+          <t>SM-966</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nesma Airlines NE-153</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1409</v>
+        <v>1140</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-46</v>
+        <v>-3</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -757,27 +757,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-440</t>
+          <t>SM-966</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-155</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1410</v>
+        <v>1140</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-45</v>
+        <v>-3</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,36 +802,36 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>22-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-440</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>flyadeal F3-911</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1410</v>
+        <v>969</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1455</v>
+        <v>1299</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-45</v>
+        <v>-330</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,36 +847,36 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-132</t>
+          <t>flynas XY-854</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1023</v>
+        <v>1009</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1143</v>
+        <v>1299</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-120</v>
+        <v>-290</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -892,12 +892,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -909,10 +909,10 @@
         <v>1024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1143</v>
+        <v>1299</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-119</v>
+        <v>-275</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,36 +937,36 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>24-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-153</t>
+          <t>Air Arabia Egypt E5-316</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1140</v>
+        <v>1119</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1143</v>
+        <v>1299</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3</v>
+        <v>-180</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1024</v>
+        <v>1140</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-275</v>
+        <v>-159</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1013,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>Nile Air NP-134</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1140</v>
+        <v>1231</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-159</v>
+        <v>-68</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1143</v>
+        <v>1231</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-156</v>
+        <v>-68</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1127,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-69</v>
+        <v>-68</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,27 +1162,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-434</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1299</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nile Air NP-132</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1231</v>
+        <v>1023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1299</v>
+        <v>1143</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-68</v>
+        <v>-120</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>24-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,26 +1262,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-854</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1430</v>
+        <v>1024</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1299</v>
+        <v>1143</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>131</v>
+        <v>-119</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1307,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>flynas XY-894</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1140</v>
+        <v>1203</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-315</v>
+        <v>60</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,30 +1352,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>flynas XY-854</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1146</v>
+        <v>1203</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1455</v>
+        <v>1143</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-309</v>
+        <v>60</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-234</t>
+          <t>Nile Air NP-232</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1409</v>
+        <v>811</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1455</v>
+        <v>868</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-46</v>
+        <v>-57</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>30</v>
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1409</v>
+        <v>811</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1455</v>
+        <v>868</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-46</v>
+        <v>-57</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>30</v>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>27-MAY-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,17 +1487,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-332</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1409</v>
+        <v>813</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1455</v>
+        <v>868</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-46</v>
+        <v>-55</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1522,27 +1522,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SM-434</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-132</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1409</v>
+        <v>615</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1455</v>
+        <v>628</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-46</v>
+        <v>-13</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>30</v>
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,26 +1577,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-854</t>
+          <t>Nesma Airlines NE-153</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1469</v>
+        <v>615</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1455</v>
+        <v>628</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>14</v>
+        <v>-13</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SM-440</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1140</v>
+        <v>615</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1143</v>
+        <v>628</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,26 +1667,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-132</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1023</v>
+        <v>811</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1026</v>
+        <v>628</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-3</v>
+        <v>183</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,26 +1712,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1024</v>
+        <v>819</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1026</v>
+        <v>628</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-2</v>
+        <v>191</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>31-MAY-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,26 +1757,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>725</v>
+        <v>853</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-143</v>
+        <v>225</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -1792,27 +1792,27 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SM-434</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-232</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>811</v>
+        <v>615</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-57</v>
+        <v>-13</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>30</v>
@@ -1837,36 +1837,36 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SM-434</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-134</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-57</v>
+        <v>199</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -1882,36 +1882,36 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SM-434</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-911</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>919</v>
+        <v>835</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>51</v>
+        <v>207</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,26 +1937,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-894</t>
+          <t>Nesma Airlines NE-151</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1010</v>
+        <v>615</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>142</v>
+        <v>-13</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>27-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,26 +1982,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-854</t>
+          <t>EgyptAir MS-688</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1010</v>
+        <v>755</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>868</v>
+        <v>628</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2027,26 +2027,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-682</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>615</v>
+        <v>755</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-13</v>
+        <v>127</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2062,36 +2062,36 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-153</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>615</v>
+        <v>827</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-13</v>
+        <v>199</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2107,36 +2107,36 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-151</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>615</v>
+        <v>835</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-13</v>
+        <v>207</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2152,27 +2152,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-688</t>
+          <t>EgyptAir MS-684</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>811</v>
+        <v>827</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2197,27 +2197,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-434</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-684</t>
+          <t>EgyptAir MS-698</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>819</v>
+        <v>835</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2242,36 +2242,36 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30-MAY-26</t>
+          <t>05-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SM-966</t>
+          <t>SM-440</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-698</t>
+          <t>Nesma Airlines NE-155</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>819</v>
+        <v>615</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>628</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>191</v>
+        <v>-13</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2279,1131 +2279,6 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-153</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-688</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="n">
-        <v>787</v>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>811</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>31-MAY-26</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n">
-        <v>819</v>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>01-JUN-26</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>01-JUN-26</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-688</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>827</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>01-JUN-26</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>835</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-688</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="n">
-        <v>755</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-682</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n">
-        <v>755</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n">
-        <v>827</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H52" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>02-JUN-26</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n">
-        <v>835</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="G53" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>03-JUN-26</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-684</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>827</v>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="G54" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>03-JUN-26</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-698</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>835</v>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H55" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>05-JUN-26</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-155</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-153</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-854</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>770</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>670</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>688</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>-18</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-232</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>679</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>688</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>12-JUN-26</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-434</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-151</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>628</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>15-JUN-26</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-894</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>778</v>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>15-JUN-26</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>SM-440</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-854</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>778</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
